--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -316,6 +316,12 @@
     <t>SNICKERS CHOCO 35G</t>
   </si>
   <si>
+    <t>10000757</t>
+  </si>
+  <si>
+    <t>L'AGIE FULL MILK 60G</t>
+  </si>
+  <si>
     <t>20054753</t>
   </si>
   <si>
@@ -346,10 +352,10 @@
     <t>DELFI CHOCO DM 2X25G</t>
   </si>
   <si>
-    <t>10000757</t>
-  </si>
-  <si>
-    <t>L'AGIE FULL MILK 60G</t>
+    <t>20120946</t>
+  </si>
+  <si>
+    <t>KINDER JOY DC COMICS</t>
   </si>
   <si>
     <t>20141135</t>
@@ -478,6 +484,12 @@
     <t>BENG-BENG SHR IT 10S</t>
   </si>
   <si>
+    <t>20141835</t>
+  </si>
+  <si>
+    <t>CADBURY OREO SHRBAG</t>
+  </si>
+  <si>
     <t>20138897</t>
   </si>
   <si>
@@ -589,12 +601,6 @@
     <t>YUPI GUMMY BB.BEAR45</t>
   </si>
   <si>
-    <t>20136192</t>
-  </si>
-  <si>
-    <t>YUPI GMY CHOP KIWI42</t>
-  </si>
-  <si>
     <t>20129720</t>
   </si>
   <si>
@@ -917,12 +923,6 @@
   </si>
   <si>
     <t>IDM CND GUMMY ORG88G</t>
-  </si>
-  <si>
-    <t>20107005</t>
-  </si>
-  <si>
-    <t>YUPI BOLI BLCKBR 40G</t>
   </si>
   <si>
     <t>10028390</t>
@@ -2268,13 +2268,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2291,7 +2291,7 @@
         <v>24</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2311,7 +2311,7 @@
         <v>24</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2331,7 +2331,7 @@
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2351,7 +2351,7 @@
         <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2371,10 +2371,10 @@
         <v>24</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2388,10 +2388,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2411,7 +2411,7 @@
         <v>42</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2431,7 +2431,7 @@
         <v>42</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2451,7 +2451,7 @@
         <v>42</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2471,7 +2471,7 @@
         <v>42</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2488,10 +2488,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2511,7 +2511,7 @@
         <v>45</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2531,7 +2531,7 @@
         <v>45</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2551,7 +2551,7 @@
         <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2571,18 +2571,18 @@
         <v>45</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2591,10 +2591,10 @@
         <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2608,33 +2608,33 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2648,10 +2648,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2668,13 +2668,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2688,10 +2688,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>74</v>
@@ -2708,10 +2708,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>74</v>
@@ -2728,10 +2728,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>74</v>
@@ -2748,13 +2748,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2768,13 +2768,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2788,10 +2788,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2799,39 +2799,39 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2848,13 +2848,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2868,10 +2868,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2888,10 +2888,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2908,13 +2908,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2928,10 +2928,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2939,39 +2939,39 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2988,10 +2988,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3008,10 +3008,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3028,10 +3028,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3048,10 +3048,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3068,10 +3068,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3088,10 +3088,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3099,19 +3099,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3148,10 +3148,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3168,10 +3168,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3188,10 +3188,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3208,13 +3208,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3228,13 +3228,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3248,10 +3248,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3268,10 +3268,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3288,10 +3288,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3299,19 +3299,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3328,10 +3328,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3348,10 +3348,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3368,13 +3368,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3388,13 +3388,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3408,10 +3408,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3428,10 +3428,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3448,10 +3448,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3468,10 +3468,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3479,19 +3479,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3508,10 +3508,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3528,10 +3528,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3548,10 +3548,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3568,10 +3568,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3588,10 +3588,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3608,10 +3608,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3619,19 +3619,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3648,13 +3648,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3668,10 +3668,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>9</v>
@@ -3688,13 +3688,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3708,10 +3708,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3728,10 +3728,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3748,10 +3748,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3759,19 +3759,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3788,13 +3788,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3808,10 +3808,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>9</v>
@@ -3828,10 +3828,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>9</v>
@@ -3848,13 +3848,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3868,33 +3868,33 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>272</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3908,13 +3908,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>272</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3928,33 +3928,33 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3968,13 +3968,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3988,13 +3988,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>272</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4008,33 +4008,33 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4048,10 +4048,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4068,10 +4068,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4088,10 +4088,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4108,10 +4108,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4119,19 +4119,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4148,13 +4148,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4168,7 +4168,7 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>15</v>
@@ -4188,7 +4188,7 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>18</v>
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>21</v>
@@ -4228,7 +4228,7 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>24</v>
@@ -4248,7 +4248,7 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>42</v>
@@ -4268,7 +4268,7 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>45</v>
@@ -4288,10 +4288,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4308,10 +4308,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4328,10 +4328,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4348,10 +4348,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4368,13 +4368,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4388,10 +4388,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
